--- a/data/trans_camb/P19C02-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C02-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 1,88</t>
+          <t>-5,68; 1,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 8,41</t>
+          <t>-1,01; 8,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 10,28</t>
+          <t>0,89; 10,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,79</t>
+          <t>1,08; 7,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 13,13</t>
+          <t>4,11; 12,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,0; 19,09</t>
+          <t>11,63; 18,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,43</t>
+          <t>-0,5; 4,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 9,45</t>
+          <t>3,07; 9,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,71; 14,08</t>
+          <t>8,4; 14,15</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 12,97</t>
+          <t>-29,76; 12,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 56,81</t>
+          <t>-5,44; 57,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 67,53</t>
+          <t>5,15; 68,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 51,57</t>
+          <t>5,41; 53,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,06; 88,69</t>
+          <t>22,73; 84,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,3; 131,13</t>
+          <t>60,68; 127,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 28,72</t>
+          <t>-3,07; 28,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,17; 62,54</t>
+          <t>17,92; 62,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48,3; 91,89</t>
+          <t>47,2; 92,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 6,05</t>
+          <t>-1,41; 5,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,0</t>
+          <t>0,48; 7,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 19,56</t>
+          <t>0,07; 19,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 5,57</t>
+          <t>-1,67; 5,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 9,4</t>
+          <t>2,25; 9,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,01; 31,29</t>
+          <t>13,26; 32,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,83</t>
+          <t>-0,26; 4,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,54</t>
+          <t>2,24; 7,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,46; 23,32</t>
+          <t>8,78; 23,04</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 20,85</t>
+          <t>-4,05; 20,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 27,5</t>
+          <t>1,33; 26,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 65,57</t>
+          <t>0,98; 66,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 17,33</t>
+          <t>-4,64; 16,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 29,71</t>
+          <t>6,17; 29,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,61; 96,03</t>
+          <t>38,29; 99,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 15,55</t>
+          <t>-0,79; 14,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,13; 24,35</t>
+          <t>6,66; 23,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,59; 74,19</t>
+          <t>26,61; 72,75</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 7,49</t>
+          <t>-5,7; 8,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 14,13</t>
+          <t>1,21; 14,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,18; 25,67</t>
+          <t>12,93; 25,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 5,81</t>
+          <t>-7,8; 5,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 9,38</t>
+          <t>-4,05; 8,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 20,0</t>
+          <t>7,71; 20,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 5,08</t>
+          <t>-4,84; 5,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 9,93</t>
+          <t>0,07; 9,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,78; 21,3</t>
+          <t>12,0; 20,89</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 19,82</t>
+          <t>-13,17; 21,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,52; 38,88</t>
+          <t>3,39; 39,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,59; 70,71</t>
+          <t>29,71; 70,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 14,83</t>
+          <t>-16,76; 13,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 24,24</t>
+          <t>-8,51; 22,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,74; 52,34</t>
+          <t>16,32; 52,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 13,09</t>
+          <t>-11,06; 12,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 25,99</t>
+          <t>0,18; 24,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,87; 55,35</t>
+          <t>26,98; 53,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 3,31</t>
+          <t>-1,36; 3,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,95</t>
+          <t>3,82; 9,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,77; 19,47</t>
+          <t>4,79; 19,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 4,82</t>
+          <t>-0,39; 4,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 10,63</t>
+          <t>5,59; 10,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,14; 29,82</t>
+          <t>16,59; 31,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,31</t>
+          <t>-0,25; 3,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,33; 9,15</t>
+          <t>5,39; 9,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,65; 22,18</t>
+          <t>12,92; 22,43</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 12,12</t>
+          <t>-4,57; 13,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,02; 33,14</t>
+          <t>12,66; 33,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,48; 69,85</t>
+          <t>18,12; 69,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 17,97</t>
+          <t>-1,31; 16,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,73; 37,88</t>
+          <t>18,27; 38,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,7; 103,88</t>
+          <t>55,27; 110,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 12,04</t>
+          <t>-0,69; 11,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,81; 32,45</t>
+          <t>18,1; 33,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43,0; 78,08</t>
+          <t>44,3; 79,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C02-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C02-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>5,92</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>16,31</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11,38</t>
+          <t>12,08</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 1,8</t>
+          <t>-5,57; 2,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 8,49</t>
+          <t>-1,5; 7,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 10,15</t>
+          <t>1,38; 10,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 7,97</t>
+          <t>1,05; 7,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 12,77</t>
+          <t>4,19; 12,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,63; 18,93</t>
+          <t>12,65; 19,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 4,4</t>
+          <t>-0,99; 4,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 9,57</t>
+          <t>3,08; 9,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,4; 14,15</t>
+          <t>9,27; 14,69</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,76; 12,28</t>
+          <t>-29,41; 16,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 57,37</t>
+          <t>-9,51; 52,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,15; 68,19</t>
+          <t>6,52; 68,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,41; 53,36</t>
+          <t>5,4; 51,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,73; 84,04</t>
+          <t>22,12; 83,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,68; 127,56</t>
+          <t>66,87; 131,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 28,06</t>
+          <t>-5,58; 28,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,92; 62,0</t>
+          <t>17,17; 60,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,2; 92,15</t>
+          <t>50,66; 94,18</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,84</t>
+          <t>18,37</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,77</t>
+          <t>17,94</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16,24</t>
+          <t>18,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 5,85</t>
+          <t>-0,66; 6,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 7,56</t>
+          <t>0,97; 7,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 19,65</t>
+          <t>14,57; 21,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 5,26</t>
+          <t>-1,57; 5,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 9,34</t>
+          <t>2,26; 9,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,26; 32,55</t>
+          <t>14,7; 21,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,61</t>
+          <t>-0,38; 4,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,4</t>
+          <t>2,53; 7,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,78; 23,04</t>
+          <t>15,6; 20,43</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>56,13%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 20,91</t>
+          <t>-2,02; 21,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 26,0</t>
+          <t>2,75; 27,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 66,3</t>
+          <t>45,05; 75,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 16,4</t>
+          <t>-4,44; 18,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 29,08</t>
+          <t>6,34; 29,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,29; 99,77</t>
+          <t>41,33; 67,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 14,81</t>
+          <t>-1,09; 14,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 23,99</t>
+          <t>7,52; 24,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,61; 72,75</t>
+          <t>46,12; 66,36</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19,22</t>
+          <t>19,46</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,12</t>
+          <t>14,11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16,72</t>
+          <t>16,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 8,01</t>
+          <t>-6,69; 7,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 14,44</t>
+          <t>1,65; 15,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,93; 25,47</t>
+          <t>13,25; 25,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 5,23</t>
+          <t>-7,96; 6,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 8,84</t>
+          <t>-3,84; 9,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 20,16</t>
+          <t>8,6; 20,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 5,0</t>
+          <t>-4,57; 4,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 9,62</t>
+          <t>-0,23; 9,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,0; 20,89</t>
+          <t>12,18; 21,7</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 21,76</t>
+          <t>-14,65; 21,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,39; 39,44</t>
+          <t>3,82; 42,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,71; 70,86</t>
+          <t>30,31; 70,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 13,94</t>
+          <t>-17,07; 16,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 22,34</t>
+          <t>-8,49; 24,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,32; 52,09</t>
+          <t>18,37; 53,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 12,65</t>
+          <t>-10,62; 12,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 24,89</t>
+          <t>-0,61; 23,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,98; 53,89</t>
+          <t>27,41; 56,74</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14,89</t>
+          <t>18,52</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,69</t>
+          <t>19,56</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17,88</t>
+          <t>19,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,73</t>
+          <t>-1,86; 3,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,82; 9,03</t>
+          <t>3,69; 9,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,79; 19,29</t>
+          <t>15,56; 21,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,65</t>
+          <t>-0,29; 4,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,59; 10,87</t>
+          <t>5,5; 10,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,59; 31,53</t>
+          <t>17,36; 21,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 3,28</t>
+          <t>-0,08; 3,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,39; 9,19</t>
+          <t>5,5; 9,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,92; 22,43</t>
+          <t>17,39; 20,69</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>65,99%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 13,62</t>
+          <t>-6,18; 12,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,66; 33,05</t>
+          <t>12,51; 32,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,12; 69,66</t>
+          <t>51,58; 77,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 16,78</t>
+          <t>-0,87; 16,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,27; 38,94</t>
+          <t>18,04; 37,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,27; 110,4</t>
+          <t>56,92; 79,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 11,83</t>
+          <t>-0,26; 11,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,1; 33,19</t>
+          <t>18,39; 32,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>44,3; 79,46</t>
+          <t>57,96; 74,16</t>
         </is>
       </c>
     </row>
